--- a/data/trans_orig/Q5413-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2007</t>
+          <t>Población según si es capaz de vestirse solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>21760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>10702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28144</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>20792</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>40388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>345802</t>
+          <t>346448</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>361447</t>
+          <t>361642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>548903</t>
+          <t>548293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>569518</t>
+          <t>569104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>898686</t>
+          <t>901393</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>926916</t>
+          <t>927853</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141928</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9764</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>23499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29237</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>9039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23108</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>9043</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24333</t>
+          <t>25025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41004</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472201</t>
+          <t>474818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>489648</t>
+          <t>489784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>634702</t>
+          <t>634090</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>657079</t>
+          <t>656918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1116905</t>
+          <t>1115491</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1142557</t>
+          <t>1142066</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,84%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2012</t>
+          <t>Población según si es capaz de vestirse solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24471</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22016</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>45292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62107</t>
+          <t>61420</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35235</t>
+          <t>35681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>51786</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81740</t>
+          <t>84394</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70779</t>
+          <t>70094</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>107605</t>
+          <t>109010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>362644</t>
+          <t>361459</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>387868</t>
+          <t>387663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>516051</t>
+          <t>516529</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>553514</t>
+          <t>554866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>890470</t>
+          <t>889507</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>936430</t>
+          <t>935283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10715</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105225</t>
+          <t>105151</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115644</t>
+          <t>115632</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,82 +3485,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>79664</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73950</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>82118</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>95,89%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>98,85%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>191220</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>182894</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>196593</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>94,79%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>90,66%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>97,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>79664</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>73612</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>82050</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>95,89%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>88,61%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>191220</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>183157</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>196643</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>90,79%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9654</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39167</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26951</t>
+          <t>25637</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>24198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48395</t>
+          <t>46828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38104</t>
+          <t>37384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67631</t>
+          <t>65821</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42030</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55323</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88450</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80512</t>
+          <t>81482</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>121364</t>
+          <t>120112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>498213</t>
+          <t>499982</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>526656</t>
+          <t>527631</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>614038</t>
+          <t>613112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>652008</t>
+          <t>653537</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1124758</t>
+          <t>1124769</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1172130</t>
+          <t>1175067</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,42%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2016</t>
+          <t>Población según si es capaz de vestirse solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>12387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31773</t>
+          <t>32435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17465</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39660</t>
+          <t>39078</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33474</t>
+          <t>32761</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28653</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>56363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49554</t>
+          <t>47109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>83017</t>
+          <t>81228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>314396</t>
+          <t>315032</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>334421</t>
+          <t>334006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>476379</t>
+          <t>475004</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>509296</t>
+          <t>509547</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>798209</t>
+          <t>797669</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>836891</t>
+          <t>837222</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,14%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179714</t>
+          <t>179468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189580</t>
+          <t>189169</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169966</t>
+          <t>169297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184149</t>
+          <t>184073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355196</t>
+          <t>354997</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371744</t>
+          <t>371696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -5755,97 +5755,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5868,97 +5868,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6964</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31890</t>
+          <t>32956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19452</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41199</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19590</t>
+          <t>19538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36511</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68287</t>
+          <t>69096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60323</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98412</t>
+          <t>99047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>540544</t>
+          <t>541486</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>562059</t>
+          <t>562115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>686353</t>
+          <t>684352</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>723219</t>
+          <t>721279</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1237316</t>
+          <t>1235444</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1279729</t>
+          <t>1276473</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de vestirse solo en 2023</t>
+          <t>Población según si es capaz de vestirse solo en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>27908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19091</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>33208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45735</t>
+          <t>45432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64776</t>
+          <t>65507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62480</t>
+          <t>61937</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86538</t>
+          <t>85558</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237482</t>
+          <t>237039</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251973</t>
+          <t>251941</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>413058</t>
+          <t>412351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>435013</t>
+          <t>436269</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>656747</t>
+          <t>655592</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>683044</t>
+          <t>683683</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>12948</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>22126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28758</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>256653</t>
+          <t>257395</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267411</t>
+          <t>267373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>431977</t>
+          <t>432182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452452</t>
+          <t>452153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>695940</t>
+          <t>695166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>720581</t>
+          <t>719709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -7810,97 +7810,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96808</t>
+          <t>97776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104670</t>
+          <t>104667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69191</t>
+          <t>68915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>168489</t>
+          <t>168421</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175705</t>
+          <t>175704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13416</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18078</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>39244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>20529</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37883</t>
+          <t>36679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32221</t>
+          <t>35503</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86357</t>
+          <t>87079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59998</t>
+          <t>61489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113282</t>
+          <t>113691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>600444</t>
+          <t>601804</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>620006</t>
+          <t>619998</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>914328</t>
+          <t>913202</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>982774</t>
+          <t>981330</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1527785</t>
+          <t>1527040</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1597443</t>
+          <t>1595506</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5413-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5413-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20792</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23688</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18985</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40388</t>
+          <t>39634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>346448</t>
+          <t>345678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>361642</t>
+          <t>361510</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>548293</t>
+          <t>548110</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>569104</t>
+          <t>569472</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>901393</t>
+          <t>900585</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>927853</t>
+          <t>926950</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,77 +1322,77 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5650</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141898</t>
+          <t>141236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>149481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23499</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>29262</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25025</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>41035</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474818</t>
+          <t>472760</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>489784</t>
+          <t>489621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>634090</t>
+          <t>634513</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>656918</t>
+          <t>657116</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1115491</t>
+          <t>1117009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1142066</t>
+          <t>1143491</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21918</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45292</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61420</t>
+          <t>62165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14725</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51786</t>
+          <t>50726</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84394</t>
+          <t>81519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70094</t>
+          <t>70436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109010</t>
+          <t>107738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>361459</t>
+          <t>363429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>387663</t>
+          <t>387364</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>516529</t>
+          <t>517349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>554866</t>
+          <t>553150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>889507</t>
+          <t>889590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>935283</t>
+          <t>934090</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>7018</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,84%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105151</t>
+          <t>104889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115632</t>
+          <t>115660</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73950</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182894</t>
+          <t>183035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196593</t>
+          <t>196427</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21246</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47724</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25637</t>
+          <t>26428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24198</t>
+          <t>24427</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37384</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65821</t>
+          <t>67384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55077</t>
+          <t>55282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85402</t>
+          <t>87353</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81482</t>
+          <t>80072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120112</t>
+          <t>120271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>499982</t>
+          <t>498251</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>527631</t>
+          <t>526582</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>613112</t>
+          <t>615243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>653537</t>
+          <t>652950</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1124769</t>
+          <t>1121949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1175067</t>
+          <t>1172150</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32435</t>
+          <t>32504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39078</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32761</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28773</t>
+          <t>26858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56363</t>
+          <t>55990</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47109</t>
+          <t>49089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81228</t>
+          <t>83800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>315032</t>
+          <t>314812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>334006</t>
+          <t>333947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>475004</t>
+          <t>475970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>509547</t>
+          <t>508004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>797669</t>
+          <t>798981</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>837222</t>
+          <t>836095</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2299</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7925</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24225</t>
+          <t>23632</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>179468</t>
+          <t>179464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>189180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169297</t>
+          <t>170263</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184073</t>
+          <t>184795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>354997</t>
+          <t>354015</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371696</t>
+          <t>370949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>67197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11962</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32956</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41795</t>
+          <t>42085</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19538</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69096</t>
+          <t>67949</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>61819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99047</t>
+          <t>98730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>541486</t>
+          <t>541312</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>562115</t>
+          <t>563135</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>684352</t>
+          <t>686593</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>721279</t>
+          <t>721351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1235444</t>
+          <t>1232944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1276473</t>
+          <t>1277194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5412</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,22 +6928,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>21435</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>15552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>29771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>27295</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33208</t>
+          <t>35355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>58833</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45432</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65507</t>
+          <t>71247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>72559</t>
+          <t>77824</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61937</t>
+          <t>66179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85558</t>
+          <t>90994</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>245844</t>
+          <t>265244</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237039</t>
+          <t>256944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251941</t>
+          <t>272086</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>425057</t>
+          <t>457596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>412351</t>
+          <t>444664</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>436269</t>
+          <t>469354</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>670901</t>
+          <t>722840</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>655592</t>
+          <t>705905</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>683683</t>
+          <t>736407</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,94%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>499908</t>
+          <t>537864</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>499908</t>
+          <t>537864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>499908</t>
+          <t>537864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>769152</t>
+          <t>827959</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769152</t>
+          <t>827959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>769152</t>
+          <t>827959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>6368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>879</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7462,67 +7462,67 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>14690</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4,84%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>11929</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>18093</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>10671</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>22126</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>14191</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29402</t>
+          <t>29004</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>263229</t>
+          <t>293347</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257395</t>
+          <t>286259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267373</t>
+          <t>297724</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>444203</t>
+          <t>264838</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>432182</t>
+          <t>258567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452153</t>
+          <t>269011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>707432</t>
+          <t>558185</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>695166</t>
+          <t>549107</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>719709</t>
+          <t>564758</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>432</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2501</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>102920</t>
+          <t>116155</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97776</t>
+          <t>110569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104667</t>
+          <t>118267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,27 +8066,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70890</t>
+          <t>82423</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68915</t>
+          <t>80805</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>173810</t>
+          <t>198578</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>168421</t>
+          <t>193006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175704</t>
+          <t>200857</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21145</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>16251</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29902</t>
+          <t>31618</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>28768</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39244</t>
+          <t>39381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>30011</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20529</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36679</t>
+          <t>40119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>65677</t>
+          <t>71194</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35503</t>
+          <t>61076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>83521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>93549</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61489</t>
+          <t>86901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113691</t>
+          <t>117758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>611992</t>
+          <t>674746</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>601804</t>
+          <t>662940</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>619998</t>
+          <t>683779</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>940150</t>
+          <t>804857</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>913202</t>
+          <t>790286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>981330</t>
+          <t>817619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1552142</t>
+          <t>1479603</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1527040</t>
+          <t>1462108</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1595506</t>
+          <t>1496085</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1026972</t>
+          <t>898365</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1026972</t>
+          <t>898365</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1026972</t>
+          <t>898365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1674459</t>
+          <t>1611166</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1674459</t>
+          <t>1611166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1674459</t>
+          <t>1611166</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
